--- a/A.Data/Series_Keys.xlsx
+++ b/A.Data/Series_Keys.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\MPFS DEPT\Quentin\Stress Tests\Quick_Stress_Testing\Meta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Filescluster\shared\MPS\WORD\MPFS DEPT\Quentin\Stress Tests\Quick_Stress_Testing\Meta\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12450" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12450" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Meta" sheetId="4" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="HP" sheetId="1" r:id="rId4"/>
     <sheet name="BondYield" sheetId="5" r:id="rId5"/>
     <sheet name="Euribor3M" sheetId="6" r:id="rId6"/>
+    <sheet name="CPI" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="152">
   <si>
     <t>RESR.Q.BE._T.N.XTR.TVAL.BE2.TB.N.IX</t>
   </si>
@@ -425,6 +426,66 @@
   </si>
   <si>
     <t>RESR.Q.LT._T.N._TR.TVAL.4D0.TB.N.IX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.AT.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.BE.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.CY.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.DE.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.EE.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.ES.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.FI.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.FR.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.GR.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.IE.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.IT.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.LU.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.LT.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.LV.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.MT.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.NL.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.PT.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.SI.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICP.M.SK.N.000000.4.ANR </t>
+  </si>
+  <si>
+    <t>ICP.M.U2.N.000000.4.INX</t>
   </si>
 </sst>
 </file>
@@ -1057,143 +1118,143 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:B21">
-    <sortCondition ref="B2:B21"/>
+  <sortState ref="A2:B22">
+    <sortCondition ref="B2:B22"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1807,6 +1868,199 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>148</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:B71">
+    <sortCondition ref="A2:A71"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Times New Roman,Regular"&amp;12&amp;K000000Central Bank of Ireland - UNRESTRICTED</oddHeader>
+    <evenHeader>&amp;L&amp;"Times New Roman,Regular"&amp;12&amp;K000000Central Bank of Ireland - UNRESTRICTED</evenHeader>
+    <firstHeader>&amp;L&amp;"Times New Roman,Regular"&amp;12&amp;K000000Central Bank of Ireland - UNRESTRICTED</firstHeader>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="a586b747-2a7c-4f57-bcd1-e81df5c8c005" origin="userSelected">
   <element uid="id_classification_nonbusiness" value=""/>
@@ -1814,7 +2068,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD7C660C-544F-4F08-893F-2B5784764B95}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7993CA38-4F13-4D46-AF62-6120A314A6B9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>

--- a/A.Data/Series_Keys.xlsx
+++ b/A.Data/Series_Keys.xlsx
@@ -485,7 +485,7 @@
     <t xml:space="preserve">ICP.M.SK.N.000000.4.ANR </t>
   </si>
   <si>
-    <t>ICP.M.U2.N.000000.4.INX</t>
+    <t>ICP.M.U2.N.000000.4.ANR</t>
   </si>
 </sst>
 </file>
@@ -2068,7 +2068,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7993CA38-4F13-4D46-AF62-6120A314A6B9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2028E59F-B536-4FD1-9BC3-5BB305F126AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>

--- a/A.Data/Series_Keys.xlsx
+++ b/A.Data/Series_Keys.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="153">
   <si>
     <t>RESR.Q.BE._T.N.XTR.TVAL.BE2.TB.N.IX</t>
   </si>
@@ -486,6 +486,9 @@
   </si>
   <si>
     <t>ICP.M.U2.N.000000.4.ANR</t>
+  </si>
+  <si>
+    <t>ICP.M.I8.N.000000.4.ANR</t>
   </si>
 </sst>
 </file>
@@ -1873,7 +1876,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.7265625" bestFit="1" customWidth="1"/>
@@ -2044,6 +2047,14 @@
         <v>151</v>
       </c>
       <c r="B21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2068,7 +2079,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2028E59F-B536-4FD1-9BC3-5BB305F126AE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC8F08B9-CB63-4146-8D00-E1B7A665876B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>

--- a/A.Data/Series_Keys.xlsx
+++ b/A.Data/Series_Keys.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12450" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12450" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Meta" sheetId="4" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet name="BondYield" sheetId="5" r:id="rId5"/>
     <sheet name="Euribor3M" sheetId="6" r:id="rId6"/>
     <sheet name="CPI" sheetId="7" r:id="rId7"/>
+    <sheet name="Demand" sheetId="8" r:id="rId8"/>
+    <sheet name="Investment" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="195">
   <si>
     <t>RESR.Q.BE._T.N.XTR.TVAL.BE2.TB.N.IX</t>
   </si>
@@ -489,6 +491,132 @@
   </si>
   <si>
     <t>ICP.M.I8.N.000000.4.ANR</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.AT.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.BE.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.CY.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.DE.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.EE.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.ES.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.FI.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.FR.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.GR.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.IE.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.IT.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.LU.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.LT.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.LV.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.MT.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.NL.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.PT.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.SI.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.SK.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.U2.W0.S1.S1.D.P3T5._Z._Z._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.AT.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.BE.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.CY.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.DE.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.EE.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.ES.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.FI.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.FR.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.GR.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.IE.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.IT.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.LU.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.LT.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.LV.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.MT.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.NL.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.PT.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.SI.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.SK.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.I8.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
+  </si>
+  <si>
+    <t>MNA.Q.Y.U2.W0.S1.S1.D.P51G.N11G._T._Z.EUR.V.N</t>
   </si>
 </sst>
 </file>
@@ -2072,6 +2200,388 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>166</v>
+      </c>
+      <c r="B14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>168</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>169</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>170</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>171</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>172</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Times New Roman,Regular"&amp;12&amp;K000000Central Bank of Ireland - UNRESTRICTED</oddHeader>
+    <evenHeader>&amp;L&amp;"Times New Roman,Regular"&amp;12&amp;K000000Central Bank of Ireland - UNRESTRICTED</evenHeader>
+    <firstHeader>&amp;L&amp;"Times New Roman,Regular"&amp;12&amp;K000000Central Bank of Ireland - UNRESTRICTED</firstHeader>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>187</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>189</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>190</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>191</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>192</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>194</v>
+      </c>
+      <c r="B22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Times New Roman,Regular"&amp;12&amp;K000000Central Bank of Ireland - UNRESTRICTED</oddHeader>
+    <evenHeader>&amp;L&amp;"Times New Roman,Regular"&amp;12&amp;K000000Central Bank of Ireland - UNRESTRICTED</evenHeader>
+    <firstHeader>&amp;L&amp;"Times New Roman,Regular"&amp;12&amp;K000000Central Bank of Ireland - UNRESTRICTED</firstHeader>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="a586b747-2a7c-4f57-bcd1-e81df5c8c005" origin="userSelected">
   <element uid="id_classification_nonbusiness" value=""/>
@@ -2079,7 +2589,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC8F08B9-CB63-4146-8D00-E1B7A665876B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDE2FB8D-8001-4E7F-8F83-67904D163E8C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
